--- a/salidas/empresas/TFC.xlsx
+++ b/salidas/empresas/TFC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>17.78286552429199</v>
+        <v>17.78287124633789</v>
       </c>
       <c r="C2" t="n">
         <v>39.04000091552734</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>17.85575294494629</v>
+        <v>17.85575675964355</v>
       </c>
       <c r="C4" t="n">
         <v>39.20000076293945</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>19.50779724121094</v>
+        <v>19.50781059265137</v>
       </c>
       <c r="C8" t="n">
         <v>41.9900016784668</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>19.88411903381348</v>
+        <v>19.88411712646484</v>
       </c>
       <c r="C9" t="n">
         <v>42.79999923706055</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.33942031860352</v>
+        <v>20.33940696716309</v>
       </c>
       <c r="C10" t="n">
         <v>43.77999877929688</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.41244888305664</v>
+        <v>20.41244316101074</v>
       </c>
       <c r="C11" t="n">
         <v>43.52000045776367</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>20.17324066162109</v>
+        <v>20.17323112487793</v>
       </c>
       <c r="C12" t="n">
         <v>43.0099983215332</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.6047477722168</v>
+        <v>20.60474967956543</v>
       </c>
       <c r="C13" t="n">
         <v>43.93000030517578</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>20.10775756835938</v>
+        <v>20.10776138305664</v>
       </c>
       <c r="C15" t="n">
         <v>42.45000076293945</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>19.43039131164551</v>
+        <v>19.43039703369141</v>
       </c>
       <c r="C16" t="n">
         <v>41.02000045776367</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>19.92001533508301</v>
+        <v>19.92000770568848</v>
       </c>
       <c r="C17" t="n">
         <v>41.61999893188477</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>20.15453720092773</v>
+        <v>20.1545352935791</v>
       </c>
       <c r="C18" t="n">
         <v>42.11000061035156</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>19.47011375427246</v>
+        <v>19.47011566162109</v>
       </c>
       <c r="C19" t="n">
         <v>40.68000030517578</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>18.11713790893555</v>
+        <v>18.11713600158691</v>
       </c>
       <c r="C20" t="n">
         <v>37.41999816894531</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>19.23553848266602</v>
+        <v>19.23553657531738</v>
       </c>
       <c r="C21" t="n">
         <v>39.72999954223633</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>19.55508041381836</v>
+        <v>19.55507850646973</v>
       </c>
       <c r="C22" t="n">
         <v>40.38999938964844</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>18.09724426269531</v>
+        <v>18.09723281860352</v>
       </c>
       <c r="C23" t="n">
         <v>36.97000122070312</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>17.66157722473145</v>
+        <v>17.66157150268555</v>
       </c>
       <c r="C24" t="n">
         <v>36.08000183105469</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>15.0133113861084</v>
+        <v>15.01331233978271</v>
       </c>
       <c r="C25" t="n">
         <v>30.67000007629395</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>18.03879928588867</v>
+        <v>18.03880310058594</v>
       </c>
       <c r="C26" t="n">
         <v>36.22000122070312</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.96698665618896</v>
+        <v>15.9669828414917</v>
       </c>
       <c r="C28" t="n">
         <v>32.06000137329102</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>17.31579399108887</v>
+        <v>17.31579780578613</v>
       </c>
       <c r="C29" t="n">
         <v>34.29000091552734</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>15.89175128936768</v>
+        <v>15.89175033569336</v>
       </c>
       <c r="C30" t="n">
         <v>31.46999931335449</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>11.49841594696045</v>
+        <v>11.49841022491455</v>
       </c>
       <c r="C31" t="n">
         <v>22.77000045776367</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>14.43303298950195</v>
+        <v>14.43303775787354</v>
       </c>
       <c r="C32" t="n">
         <v>28.02000045776367</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>15.45293426513672</v>
+        <v>15.45293235778809</v>
       </c>
       <c r="C33" t="n">
         <v>30</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>19.4706916809082</v>
+        <v>19.47069358825684</v>
       </c>
       <c r="C34" t="n">
         <v>37.79999923706055</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>15.65131664276123</v>
+        <v>15.65132331848145</v>
       </c>
       <c r="C36" t="n">
         <v>29.96999931335449</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.34052181243896</v>
+        <v>14.34051322937012</v>
       </c>
       <c r="C37" t="n">
         <v>27.45999908447266</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>10.52766895294189</v>
+        <v>10.52766799926758</v>
       </c>
       <c r="C38" t="n">
         <v>19.79000091552734</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.580661773681641</v>
+        <v>8.580658912658691</v>
       </c>
       <c r="C39" t="n">
         <v>16.1299991607666</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>9.000917434692383</v>
+        <v>9.00091552734375</v>
       </c>
       <c r="C40" t="n">
         <v>16.92000007629395</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>12.76166248321533</v>
+        <v>12.76166152954102</v>
       </c>
       <c r="C41" t="n">
         <v>23.34000015258789</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>12.01805305480957</v>
+        <v>12.0180549621582</v>
       </c>
       <c r="C43" t="n">
         <v>21.97999954223633</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>15.3875732421875</v>
+        <v>15.38757514953613</v>
       </c>
       <c r="C45" t="n">
         <v>27.94000053405762</v>
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>13.23961544036865</v>
+        <v>13.23962116241455</v>
       </c>
       <c r="C47" t="n">
         <v>23.90999984741211</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>13.78780937194824</v>
+        <v>13.78780746459961</v>
       </c>
       <c r="C48" t="n">
         <v>24.89999961853027</v>
@@ -1381,11 +1393,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>14.04806041717529</v>
+        <v>14.04805755615234</v>
       </c>
       <c r="C49" t="n">
         <v>25.3700008392334</v>
@@ -1406,11 +1418,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>15.52130889892578</v>
+        <v>15.52130126953125</v>
       </c>
       <c r="C50" t="n">
         <v>27.8700008392334</v>
@@ -1431,7 +1443,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1456,7 +1468,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1481,11 +1493,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>18.59515190124512</v>
+        <v>18.59514617919922</v>
       </c>
       <c r="C53" t="n">
         <v>33.2400016784668</v>
@@ -1506,11 +1518,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>16.91688346862793</v>
+        <v>16.91688537597656</v>
       </c>
       <c r="C54" t="n">
         <v>30.23999977111816</v>
@@ -1531,11 +1543,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.71836090087891</v>
+        <v>14.71835899353027</v>
       </c>
       <c r="C55" t="n">
         <v>26.30999946594238</v>
@@ -1556,11 +1568,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>13.96940326690674</v>
+        <v>13.96939945220947</v>
       </c>
       <c r="C56" t="n">
         <v>24.82999992370605</v>
@@ -1581,11 +1593,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>12.44475078582764</v>
+        <v>12.44474983215332</v>
       </c>
       <c r="C57" t="n">
         <v>22.1200008392334</v>
@@ -1606,11 +1618,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>13.54744625091553</v>
+        <v>13.54745388031006</v>
       </c>
       <c r="C58" t="n">
         <v>24.07999992370605</v>
@@ -1631,11 +1643,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>13.25396728515625</v>
+        <v>13.25396919250488</v>
       </c>
       <c r="C59" t="n">
         <v>23.40999984741211</v>
@@ -1656,11 +1668,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>13.13507652282715</v>
+        <v>13.13507843017578</v>
       </c>
       <c r="C60" t="n">
         <v>23.20000076293945</v>
@@ -1681,11 +1693,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>14.88453197479248</v>
+        <v>14.8845272064209</v>
       </c>
       <c r="C61" t="n">
         <v>26.29000091552734</v>
@@ -1706,11 +1718,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>15.73680210113525</v>
+        <v>15.73680973052979</v>
       </c>
       <c r="C62" t="n">
         <v>27.63999938964844</v>
@@ -1731,11 +1743,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>15.71403121948242</v>
+        <v>15.71403217315674</v>
       </c>
       <c r="C63" t="n">
         <v>27.60000038146973</v>
@@ -1760,11 +1772,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>15.62863826751709</v>
+        <v>15.62863063812256</v>
       </c>
       <c r="C64" t="n">
         <v>27.45000076293945</v>
@@ -1789,11 +1801,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>15.42238521575928</v>
+        <v>15.42238903045654</v>
       </c>
       <c r="C65" t="n">
         <v>26.92000007629395</v>
@@ -1818,11 +1830,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>15.77758026123047</v>
+        <v>15.77758121490479</v>
       </c>
       <c r="C66" t="n">
         <v>27.54000091552734</v>
@@ -1847,7 +1859,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1876,11 +1888,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>14.79926872253418</v>
+        <v>14.79926776885986</v>
       </c>
       <c r="C68" t="n">
         <v>25.68000030517578</v>
@@ -1905,11 +1917,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>12.84562587738037</v>
+        <v>12.84562683105469</v>
       </c>
       <c r="C69" t="n">
         <v>22.29000091552734</v>
@@ -1934,11 +1946,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>12.29238605499268</v>
+        <v>12.29238128662109</v>
       </c>
       <c r="C70" t="n">
         <v>21.32999992370605</v>
@@ -1963,11 +1975,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>13.54751014709473</v>
+        <v>13.54750633239746</v>
       </c>
       <c r="C71" t="n">
         <v>23.34000015258789</v>
@@ -1992,11 +2004,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>13.44883155822754</v>
+        <v>13.44883346557617</v>
       </c>
       <c r="C72" t="n">
         <v>23.17000007629395</v>
@@ -2021,11 +2033,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>14.60971450805664</v>
+        <v>14.60971355438232</v>
       </c>
       <c r="C73" t="n">
         <v>25.17000007629395</v>
@@ -2050,11 +2062,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>15.88046169281006</v>
+        <v>15.88046550750732</v>
       </c>
       <c r="C74" t="n">
         <v>27.19000053405762</v>
@@ -2079,11 +2091,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>17.08362007141113</v>
+        <v>17.08360862731934</v>
       </c>
       <c r="C75" t="n">
         <v>29.25</v>
@@ -2108,7 +2120,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2137,11 +2149,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>18.83198165893555</v>
+        <v>18.83197784423828</v>
       </c>
       <c r="C77" t="n">
         <v>32.04000091552734</v>
@@ -2166,7 +2178,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2195,11 +2207,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>18.13254165649414</v>
+        <v>18.13253784179688</v>
       </c>
       <c r="C79" t="n">
         <v>30.85000038146973</v>
@@ -2224,11 +2236,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.55748558044434</v>
+        <v>18.5574779510498</v>
       </c>
       <c r="C80" t="n">
         <v>31.3700008392334</v>
@@ -2253,11 +2265,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>18.65804481506348</v>
+        <v>18.65805053710938</v>
       </c>
       <c r="C81" t="n">
         <v>31.54000091552734</v>
@@ -2282,7 +2294,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2311,11 +2323,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.23031044006348</v>
+        <v>17.23031234741211</v>
       </c>
       <c r="C83" t="n">
         <v>28.95000076293945</v>
@@ -2340,11 +2352,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>16.76607894897461</v>
+        <v>16.76607513427734</v>
       </c>
       <c r="C84" t="n">
         <v>28.17000007629395</v>
@@ -2369,11 +2381,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>17.32554054260254</v>
+        <v>17.32554244995117</v>
       </c>
       <c r="C85" t="n">
         <v>29.11000061035156</v>
@@ -2398,11 +2410,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>18.14656829833984</v>
+        <v>18.14657402038574</v>
       </c>
       <c r="C86" t="n">
         <v>30.28000068664551</v>
@@ -2427,11 +2439,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>18.3304328918457</v>
+        <v>18.3304271697998</v>
       </c>
       <c r="C87" t="n">
         <v>30.36000061035156</v>
@@ -2456,11 +2468,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>18.95230865478516</v>
+        <v>18.95231056213379</v>
       </c>
       <c r="C88" t="n">
         <v>31.38999938964844</v>
@@ -2485,7 +2497,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2514,11 +2526,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>20.02222442626953</v>
+        <v>20.02221488952637</v>
       </c>
       <c r="C90" t="n">
         <v>32.91999816894531</v>
@@ -2543,7 +2555,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2572,11 +2584,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>21.70695495605469</v>
+        <v>21.70695686340332</v>
       </c>
       <c r="C92" t="n">
         <v>35.68999862670898</v>
@@ -2601,11 +2613,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>20.78726577758789</v>
+        <v>20.78726959228516</v>
       </c>
       <c r="C93" t="n">
         <v>33.95999908447266</v>
@@ -2630,11 +2642,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>20.65872764587402</v>
+        <v>20.65872955322266</v>
       </c>
       <c r="C94" t="n">
         <v>33.75</v>
@@ -2659,11 +2671,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>20.79339790344238</v>
+        <v>20.79339218139648</v>
       </c>
       <c r="C95" t="n">
         <v>33.97000122070312</v>
@@ -2688,11 +2700,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>21.4110221862793</v>
+        <v>21.41101837158203</v>
       </c>
       <c r="C96" t="n">
         <v>34.7400016784668</v>
@@ -2717,7 +2729,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2746,7 +2758,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2775,11 +2787,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>23.44026565551758</v>
+        <v>23.44026947021484</v>
       </c>
       <c r="C99" t="n">
         <v>37.79999923706055</v>
@@ -2804,11 +2816,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>24.90993690490723</v>
+        <v>24.90994071960449</v>
       </c>
       <c r="C100" t="n">
         <v>40.16999816894531</v>
@@ -2833,7 +2845,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2862,11 +2874,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>23.6645393371582</v>
+        <v>23.66454124450684</v>
       </c>
       <c r="C102" t="n">
         <v>37.91999816894531</v>
@@ -2891,11 +2903,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>24.60688209533691</v>
+        <v>24.60688018798828</v>
       </c>
       <c r="C103" t="n">
         <v>39.43000030517578</v>
@@ -2920,11 +2932,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>23.10288238525391</v>
+        <v>23.10287094116211</v>
       </c>
       <c r="C104" t="n">
         <v>37.02000045776367</v>
@@ -2949,11 +2961,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>23.45075035095215</v>
+        <v>23.45074462890625</v>
       </c>
       <c r="C105" t="n">
         <v>37.33000183105469</v>
@@ -2978,11 +2990,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>23.37535858154297</v>
+        <v>23.37536239624023</v>
       </c>
       <c r="C106" t="n">
         <v>37.20999908447266</v>
@@ -3007,11 +3019,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>23.7962703704834</v>
+        <v>23.7962646484375</v>
       </c>
       <c r="C107" t="n">
         <v>37.88000106811523</v>
@@ -3036,11 +3048,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>23.76449394226074</v>
+        <v>23.76449775695801</v>
       </c>
       <c r="C108" t="n">
         <v>37.59000015258789</v>
@@ -3065,11 +3077,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>24.58635139465332</v>
+        <v>24.58634948730469</v>
       </c>
       <c r="C109" t="n">
         <v>38.88999938964844</v>
@@ -3094,11 +3106,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>22.3104305267334</v>
+        <v>22.31042671203613</v>
       </c>
       <c r="C110" t="n">
         <v>35.29000091552734</v>
@@ -3123,11 +3135,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>24.20897674560547</v>
+        <v>24.20896911621094</v>
       </c>
       <c r="C111" t="n">
         <v>38.04999923706055</v>
@@ -3152,11 +3164,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>24.80703544616699</v>
+        <v>24.80703926086426</v>
       </c>
       <c r="C112" t="n">
         <v>38.9900016784668</v>
@@ -3181,11 +3193,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>24.36167144775391</v>
+        <v>24.36167335510254</v>
       </c>
       <c r="C113" t="n">
         <v>38.29000091552734</v>
@@ -3210,11 +3222,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>25.2869701385498</v>
+        <v>25.28695487976074</v>
       </c>
       <c r="C114" t="n">
         <v>39.47000122070312</v>
@@ -3239,11 +3251,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>25.82510948181152</v>
+        <v>25.82511711120605</v>
       </c>
       <c r="C115" t="n">
         <v>40.31000137329102</v>
@@ -3268,11 +3280,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>25.79949760437012</v>
+        <v>25.79949378967285</v>
       </c>
       <c r="C116" t="n">
         <v>40.27000045776367</v>
@@ -3297,11 +3309,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>23.81316566467285</v>
+        <v>23.81316947937012</v>
       </c>
       <c r="C117" t="n">
         <v>36.91999816894531</v>
@@ -3326,7 +3338,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3355,11 +3367,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>23.96151733398438</v>
+        <v>23.96152877807617</v>
       </c>
       <c r="C119" t="n">
         <v>37.15000152587891</v>
@@ -3384,11 +3396,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>25.08489227294922</v>
+        <v>25.08489799499512</v>
       </c>
       <c r="C120" t="n">
         <v>38.61999893188477</v>
@@ -3413,11 +3425,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>24.55878067016602</v>
+        <v>24.55877876281738</v>
       </c>
       <c r="C121" t="n">
         <v>37.81000137329102</v>
@@ -3442,11 +3454,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>21.21368980407715</v>
+        <v>21.21369934082031</v>
       </c>
       <c r="C122" t="n">
         <v>32.65999984741211</v>
@@ -3471,11 +3483,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>21.06894493103027</v>
+        <v>21.06895065307617</v>
       </c>
       <c r="C123" t="n">
         <v>32.15999984741211</v>
@@ -3500,11 +3512,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>21.79613876342773</v>
+        <v>21.796142578125</v>
       </c>
       <c r="C124" t="n">
         <v>33.27000045776367</v>
@@ -3529,11 +3541,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>23.17845344543457</v>
+        <v>23.1784553527832</v>
       </c>
       <c r="C125" t="n">
         <v>35.38000106811523</v>
@@ -3558,11 +3570,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>24.02269172668457</v>
+        <v>24.02268600463867</v>
       </c>
       <c r="C126" t="n">
         <v>36.36999893188477</v>
@@ -3587,7 +3599,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3616,11 +3628,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>24.35294342041016</v>
+        <v>24.35293579101562</v>
       </c>
       <c r="C128" t="n">
         <v>36.86999893188477</v>
@@ -3645,11 +3657,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>25.63191986083984</v>
+        <v>25.63192367553711</v>
       </c>
       <c r="C129" t="n">
         <v>38.5</v>
@@ -3674,11 +3686,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>25.11263084411621</v>
+        <v>25.11263465881348</v>
       </c>
       <c r="C130" t="n">
         <v>37.72000122070312</v>
@@ -3703,11 +3715,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>26.09796333312988</v>
+        <v>26.09796905517578</v>
       </c>
       <c r="C131" t="n">
         <v>39.20000076293945</v>
@@ -3732,11 +3744,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>30.35733985900879</v>
+        <v>30.35732841491699</v>
       </c>
       <c r="C132" t="n">
         <v>45.25</v>
@@ -3761,7 +3773,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3790,11 +3802,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>30.98795700073242</v>
+        <v>30.98796463012695</v>
       </c>
       <c r="C134" t="n">
         <v>46.18999862670898</v>
@@ -3819,11 +3831,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>32.56041717529297</v>
+        <v>32.56040954589844</v>
       </c>
       <c r="C135" t="n">
         <v>48.22000122070312</v>
@@ -3848,11 +3860,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>30.18354606628418</v>
+        <v>30.18354797363281</v>
       </c>
       <c r="C136" t="n">
         <v>44.70000076293945</v>
@@ -3877,11 +3889,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>29.15717124938965</v>
+        <v>29.15716552734375</v>
       </c>
       <c r="C137" t="n">
         <v>43.18000030517578</v>
@@ -3906,11 +3918,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>28.31948661804199</v>
+        <v>28.31948089599609</v>
       </c>
       <c r="C138" t="n">
         <v>41.65000152587891</v>
@@ -3935,11 +3947,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>30.87606048583984</v>
+        <v>30.87605857849121</v>
       </c>
       <c r="C139" t="n">
         <v>45.40999984741211</v>
@@ -3964,11 +3976,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>32.17473983764648</v>
+        <v>32.17473602294922</v>
       </c>
       <c r="C140" t="n">
         <v>47.31999969482422</v>
@@ -3993,11 +4005,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>31.55423927307129</v>
+        <v>31.55422019958496</v>
       </c>
       <c r="C141" t="n">
         <v>46.09000015258789</v>
@@ -4022,7 +4034,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4051,11 +4063,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>33.71079635620117</v>
+        <v>33.71078109741211</v>
       </c>
       <c r="C143" t="n">
         <v>49.2400016784668</v>
@@ -4080,7 +4092,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4109,11 +4121,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>34.27627944946289</v>
+        <v>34.27628707885742</v>
       </c>
       <c r="C145" t="n">
         <v>49.72000122070312</v>
@@ -4138,11 +4150,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>38.04723358154297</v>
+        <v>38.0472412109375</v>
       </c>
       <c r="C146" t="n">
         <v>55.18999862670898</v>
@@ -4167,11 +4179,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>37.69929122924805</v>
+        <v>37.69930267333984</v>
       </c>
       <c r="C147" t="n">
         <v>54.34999847412109</v>
@@ -4196,7 +4208,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4225,7 +4237,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4254,11 +4266,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>36.69684982299805</v>
+        <v>36.69684219360352</v>
       </c>
       <c r="C150" t="n">
         <v>52.5</v>
@@ -4283,11 +4295,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>35.25693511962891</v>
+        <v>35.25693130493164</v>
       </c>
       <c r="C151" t="n">
         <v>50.43999862670898</v>
@@ -4312,11 +4324,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>35.51556015014648</v>
+        <v>35.51557159423828</v>
       </c>
       <c r="C152" t="n">
         <v>50.81000137329102</v>
@@ -4341,11 +4353,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>36.39308547973633</v>
+        <v>36.39310836791992</v>
       </c>
       <c r="C153" t="n">
         <v>51.65999984741211</v>
@@ -4370,11 +4382,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>34.19514465332031</v>
+        <v>34.19514083862305</v>
       </c>
       <c r="C154" t="n">
         <v>48.54000091552734</v>
@@ -4399,11 +4411,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>34.63190841674805</v>
+        <v>34.63191223144531</v>
       </c>
       <c r="C155" t="n">
         <v>49.15999984741211</v>
@@ -4428,11 +4440,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>36.29167175292969</v>
+        <v>36.29166793823242</v>
       </c>
       <c r="C156" t="n">
         <v>51.09999847412109</v>
@@ -4457,11 +4469,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>30.76624298095703</v>
+        <v>30.7662410736084</v>
       </c>
       <c r="C157" t="n">
         <v>43.31999969482422</v>
@@ -4486,11 +4498,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>34.65818405151367</v>
+        <v>34.65817642211914</v>
       </c>
       <c r="C158" t="n">
         <v>48.79999923706055</v>
@@ -4515,11 +4527,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>36.4915885925293</v>
+        <v>36.49160003662109</v>
       </c>
       <c r="C159" t="n">
         <v>50.97000122070312</v>
@@ -4544,11 +4556,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>33.31282043457031</v>
+        <v>33.31281280517578</v>
       </c>
       <c r="C160" t="n">
         <v>46.52999877929688</v>
@@ -4573,7 +4585,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4602,7 +4614,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4631,11 +4643,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>35.47212982177734</v>
+        <v>35.47213363647461</v>
       </c>
       <c r="C163" t="n">
         <v>49.13000106811523</v>
@@ -4660,11 +4672,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>37.20493316650391</v>
+        <v>37.20493698120117</v>
       </c>
       <c r="C164" t="n">
         <v>51.52999877929688</v>
@@ -4689,7 +4701,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4718,11 +4730,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>38.90867614746094</v>
+        <v>38.90866851806641</v>
       </c>
       <c r="C166" t="n">
         <v>53.36999893188477</v>
@@ -4747,11 +4759,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>38.67539215087891</v>
+        <v>38.67538452148438</v>
       </c>
       <c r="C167" t="n">
         <v>53.04999923706055</v>
@@ -4776,11 +4788,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>40.22046661376953</v>
+        <v>40.22045516967773</v>
       </c>
       <c r="C168" t="n">
         <v>54.72000122070312</v>
@@ -4805,11 +4817,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>41.39650344848633</v>
+        <v>41.39649963378906</v>
       </c>
       <c r="C169" t="n">
         <v>56.31999969482422</v>
@@ -4834,11 +4846,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>37.90514755249023</v>
+        <v>37.90512466430664</v>
       </c>
       <c r="C170" t="n">
         <v>51.56999969482422</v>
@@ -4863,11 +4875,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>34.19663619995117</v>
+        <v>34.19663238525391</v>
       </c>
       <c r="C171" t="n">
         <v>46.13999938964844</v>
@@ -4892,7 +4904,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4921,11 +4933,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>27.65969467163086</v>
+        <v>27.65968894958496</v>
       </c>
       <c r="C173" t="n">
         <v>37.31999969482422</v>
@@ -4950,11 +4962,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>27.65289306640625</v>
+        <v>27.65288734436035</v>
       </c>
       <c r="C174" t="n">
         <v>36.77999877929688</v>
@@ -4979,11 +4991,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>28.2318058013916</v>
+        <v>28.2318115234375</v>
       </c>
       <c r="C175" t="n">
         <v>37.54999923706055</v>
@@ -5008,11 +5020,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>28.16414833068848</v>
+        <v>28.16414260864258</v>
       </c>
       <c r="C176" t="n">
         <v>37.45999908447266</v>
@@ -5037,11 +5049,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>29.50448036193848</v>
+        <v>29.50447082519531</v>
       </c>
       <c r="C177" t="n">
         <v>38.81000137329102</v>
@@ -5066,11 +5078,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>28.92670059204102</v>
+        <v>28.92670249938965</v>
       </c>
       <c r="C178" t="n">
         <v>38.04999923706055</v>
@@ -5095,7 +5107,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5124,11 +5136,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>35.61812210083008</v>
+        <v>35.61812973022461</v>
       </c>
       <c r="C180" t="n">
         <v>46.41999816894531</v>
@@ -5153,7 +5165,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5182,11 +5194,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>36.81512832641602</v>
+        <v>36.81512069702148</v>
       </c>
       <c r="C182" t="n">
         <v>47.97999954223633</v>
@@ -5211,11 +5223,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>44.07475280761719</v>
+        <v>44.07475662231445</v>
       </c>
       <c r="C183" t="n">
         <v>56.95999908447266</v>
@@ -5240,11 +5252,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>45.12709426879883</v>
+        <v>45.12710189819336</v>
       </c>
       <c r="C184" t="n">
         <v>58.31999969482422</v>
@@ -5269,11 +5281,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>45.89315032958984</v>
+        <v>45.89315414428711</v>
       </c>
       <c r="C185" t="n">
         <v>59.31000137329102</v>
@@ -5298,11 +5310,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>48.16801452636719</v>
+        <v>48.16801834106445</v>
       </c>
       <c r="C186" t="n">
         <v>61.77999877929688</v>
@@ -5327,11 +5339,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>43.27169036865234</v>
+        <v>43.27168273925781</v>
       </c>
       <c r="C187" t="n">
         <v>55.5</v>
@@ -5356,7 +5368,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5385,11 +5397,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>44.85375595092773</v>
+        <v>44.8537483215332</v>
       </c>
       <c r="C189" t="n">
         <v>57.06000137329102</v>
@@ -5414,7 +5426,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5443,7 +5455,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5472,11 +5484,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>46.97069931030273</v>
+        <v>46.97068023681641</v>
       </c>
       <c r="C192" t="n">
         <v>59.31000137329102</v>
@@ -5501,11 +5513,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>46.36880493164062</v>
+        <v>46.36881256103516</v>
       </c>
       <c r="C193" t="n">
         <v>58.54999923706055</v>
@@ -5530,11 +5542,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>49.75043487548828</v>
+        <v>49.75044631958008</v>
       </c>
       <c r="C194" t="n">
         <v>62.81999969482422</v>
@@ -5559,11 +5571,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>49.63903045654297</v>
+        <v>49.6390380859375</v>
       </c>
       <c r="C195" t="n">
         <v>62.22000122070312</v>
@@ -5588,11 +5600,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>45.23519134521484</v>
+        <v>45.23519515991211</v>
       </c>
       <c r="C196" t="n">
         <v>56.70000076293945</v>
@@ -5617,11 +5629,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>38.57357025146484</v>
+        <v>38.57357788085938</v>
       </c>
       <c r="C197" t="n">
         <v>48.34999847412109</v>
@@ -5646,11 +5658,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>40.09328460693359</v>
+        <v>40.09328842163086</v>
       </c>
       <c r="C198" t="n">
         <v>49.7400016784668</v>
@@ -5675,11 +5687,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>38.23128890991211</v>
+        <v>38.23129272460938</v>
       </c>
       <c r="C199" t="n">
         <v>47.43000030517578</v>
@@ -5704,11 +5716,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>40.68170547485352</v>
+        <v>40.68170928955078</v>
       </c>
       <c r="C200" t="n">
         <v>50.47000122070312</v>
@@ -5733,11 +5745,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>38.14542388916016</v>
+        <v>38.14541625976562</v>
       </c>
       <c r="C201" t="n">
         <v>46.84000015258789</v>
@@ -5762,11 +5774,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>35.45796966552734</v>
+        <v>35.45797348022461</v>
       </c>
       <c r="C202" t="n">
         <v>43.54000091552734</v>
@@ -5791,11 +5803,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>36.47594451904297</v>
+        <v>36.4759407043457</v>
       </c>
       <c r="C203" t="n">
         <v>44.79000091552734</v>
@@ -5820,11 +5832,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>38.57181167602539</v>
+        <v>38.57180786132812</v>
       </c>
       <c r="C204" t="n">
         <v>46.81000137329102</v>
@@ -5849,11 +5861,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>35.45706558227539</v>
+        <v>35.45705413818359</v>
       </c>
       <c r="C205" t="n">
         <v>43.02999877929688</v>
@@ -5878,11 +5890,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>40.69774627685547</v>
+        <v>40.69775009155273</v>
       </c>
       <c r="C206" t="n">
         <v>49.38999938964844</v>
@@ -5907,11 +5919,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>39.09992218017578</v>
+        <v>39.09991836547852</v>
       </c>
       <c r="C207" t="n">
         <v>46.95000076293945</v>
@@ -5936,11 +5948,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>28.39844703674316</v>
+        <v>28.39845275878906</v>
       </c>
       <c r="C208" t="n">
         <v>34.09999847412109</v>
@@ -5965,11 +5977,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>27.13259506225586</v>
+        <v>27.13259887695312</v>
       </c>
       <c r="C209" t="n">
         <v>32.58000183105469</v>
@@ -5994,11 +6006,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>25.85731887817383</v>
+        <v>25.85732078552246</v>
       </c>
       <c r="C210" t="n">
         <v>30.46999931335449</v>
@@ -6023,7 +6035,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6052,11 +6064,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>28.19101333618164</v>
+        <v>28.19100952148438</v>
       </c>
       <c r="C212" t="n">
         <v>33.22000122070312</v>
@@ -6081,11 +6093,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>26.36078453063965</v>
+        <v>26.36078643798828</v>
       </c>
       <c r="C213" t="n">
         <v>30.54999923706055</v>
@@ -6110,11 +6122,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>24.68681526184082</v>
+        <v>24.68681144714355</v>
       </c>
       <c r="C214" t="n">
         <v>28.61000061035156</v>
@@ -6139,11 +6151,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>24.47109222412109</v>
+        <v>24.47109031677246</v>
       </c>
       <c r="C215" t="n">
         <v>28.36000061035156</v>
@@ -6168,11 +6180,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>28.21538543701172</v>
+        <v>28.21538734436035</v>
       </c>
       <c r="C216" t="n">
         <v>32.13999938964844</v>
@@ -6197,7 +6209,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6226,7 +6238,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6255,11 +6267,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>31.15853691101074</v>
+        <v>31.15853881835938</v>
       </c>
       <c r="C219" t="n">
         <v>34.97999954223633</v>
@@ -6282,11 +6294,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>34.7215461730957</v>
+        <v>34.72154235839844</v>
       </c>
       <c r="C220" t="n">
         <v>38.97999954223633</v>
@@ -6309,11 +6321,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>33.44777679443359</v>
+        <v>33.44777297973633</v>
       </c>
       <c r="C221" t="n">
         <v>37.54999923706055</v>
@@ -6336,11 +6348,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>34.07576370239258</v>
+        <v>34.07575988769531</v>
       </c>
       <c r="C222" t="n">
         <v>37.75</v>
@@ -6363,11 +6375,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>35.06870651245117</v>
+        <v>35.06869888305664</v>
       </c>
       <c r="C223" t="n">
         <v>38.84999847412109</v>
@@ -6390,7 +6402,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6417,7 +6429,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6444,11 +6456,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>39.09033203125</v>
+        <v>39.09032821655273</v>
       </c>
       <c r="C226" t="n">
         <v>42.77000045776367</v>
@@ -6471,11 +6483,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>39.34624099731445</v>
+        <v>39.34624862670898</v>
       </c>
       <c r="C227" t="n">
         <v>43.04999923706055</v>
@@ -6498,7 +6510,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6525,7 +6537,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6552,7 +6564,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6579,7 +6591,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6608,11 +6620,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>38.46840286254883</v>
+        <v>38.4683952331543</v>
       </c>
       <c r="C232" t="n">
         <v>41.15000152587891</v>
@@ -6637,11 +6649,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>35.84151458740234</v>
+        <v>35.84151840209961</v>
       </c>
       <c r="C233" t="n">
         <v>38.34000015258789</v>
@@ -6666,11 +6678,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>37.41776657104492</v>
+        <v>37.41776275634766</v>
       </c>
       <c r="C234" t="n">
         <v>39.5</v>
@@ -6695,7 +6707,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6724,7 +6736,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6753,11 +6765,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>44.896728515625</v>
+        <v>44.89672470092773</v>
       </c>
       <c r="C237" t="n">
         <v>46.81999969482422</v>
@@ -6782,7 +6794,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6811,11 +6823,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>42.79668807983398</v>
+        <v>42.79668426513672</v>
       </c>
       <c r="C239" t="n">
         <v>44.63000106811523</v>
@@ -6840,7 +6852,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6869,7 +6881,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6898,7 +6910,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6927,7 +6939,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6956,7 +6968,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6985,7 +6997,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7014,7 +7026,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7043,7 +7055,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7072,7 +7084,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7101,7 +7113,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7130,32 +7142,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>47</v>
+        <v>47.18000030517578</v>
       </c>
       <c r="C250" t="n">
-        <v>47</v>
+        <v>47.18000030517578</v>
       </c>
       <c r="D250" t="n">
-        <v>125983100</v>
+        <v>132353900</v>
       </c>
       <c r="E250" t="n">
         <v>4.37</v>
       </c>
       <c r="F250" t="n">
-        <v>10.75514874141876</v>
+        <v>10.79633874260315</v>
       </c>
       <c r="G250" t="n">
         <v>1221626188</v>
       </c>
       <c r="H250" t="n">
-        <v>57416430836</v>
+        <v>57636323922.65073</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1031273733630864</v>
+        <v>0.1083423892677717</v>
       </c>
     </row>
   </sheetData>
@@ -7187,75 +7199,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40038</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7291,13 +7303,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7333,13 +7345,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40038</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7417,13 +7429,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7459,13 +7471,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40423</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7543,13 +7555,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40491</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7585,13 +7597,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7618,7 +7630,7 @@
       <c r="I10" t="n">
         <v>1.16</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7631,13 +7643,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7664,7 +7676,7 @@
       <c r="I11" t="n">
         <v>1.21</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K11" t="n">
@@ -7677,13 +7689,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7710,7 +7722,7 @@
       <c r="I12" t="n">
         <v>1.35</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="K12" t="n">
@@ -7723,13 +7735,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7756,7 +7768,7 @@
       <c r="I13" t="n">
         <v>1.57</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="K13" t="n">
@@ -7769,13 +7781,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7802,7 +7814,7 @@
       <c r="I14" t="n">
         <v>1.83</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K14" t="n">
@@ -7815,13 +7827,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7848,7 +7860,7 @@
       <c r="I15" t="n">
         <v>2.12</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K15" t="n">
@@ -7861,13 +7873,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7894,7 +7906,7 @@
       <c r="I16" t="n">
         <v>2.4</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="K16" t="n">
@@ -7907,13 +7919,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7940,7 +7952,7 @@
       <c r="I17" t="n">
         <v>2.54</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K17" t="n">
@@ -7953,13 +7965,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7986,7 +7998,7 @@
       <c r="I18" t="n">
         <v>2.7</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K18" t="n">
@@ -7999,13 +8011,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8032,7 +8044,7 @@
       <c r="I19" t="n">
         <v>2.38</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K19" t="n">
@@ -8045,13 +8057,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8078,7 +8090,7 @@
       <c r="I20" t="n">
         <v>2.43</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K20" t="n">
@@ -8091,13 +8103,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8124,7 +8136,7 @@
       <c r="I21" t="n">
         <v>2.14</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="K21" t="n">
@@ -8137,13 +8149,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8170,7 +8182,7 @@
       <c r="I22" t="n">
         <v>2.19</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="K22" t="n">
@@ -8183,13 +8195,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8216,7 +8228,7 @@
       <c r="I23" t="n">
         <v>2.59</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="K23" t="n">
@@ -8229,13 +8241,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41848</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8262,7 +8274,7 @@
       <c r="I24" t="n">
         <v>2.399999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41848</v>
       </c>
       <c r="K24" t="n">
@@ -8275,13 +8287,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41939</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8308,7 +8320,7 @@
       <c r="I25" t="n">
         <v>2.739999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41939</v>
       </c>
       <c r="K25" t="n">
@@ -8321,13 +8333,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8354,7 +8366,7 @@
       <c r="I26" t="n">
         <v>2.75</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K26" t="n">
@@ -8367,13 +8379,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42121</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8400,7 +8412,7 @@
       <c r="I27" t="n">
         <v>2.73</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42121</v>
       </c>
       <c r="K27" t="n">
@@ -8413,13 +8425,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8446,7 +8458,7 @@
       <c r="I28" t="n">
         <v>2.77</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="K28" t="n">
@@ -8459,13 +8471,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8492,7 +8504,7 @@
       <c r="I29" t="n">
         <v>2.7</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K29" t="n">
@@ -8505,13 +8517,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8538,7 +8550,7 @@
       <c r="I30" t="n">
         <v>2.56</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K30" t="n">
@@ -8551,13 +8563,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8584,7 +8596,7 @@
       <c r="I31" t="n">
         <v>2.56</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="K31" t="n">
@@ -8597,13 +8609,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8630,7 +8642,7 @@
       <c r="I32" t="n">
         <v>2.6</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K32" t="n">
@@ -8643,13 +8655,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42667</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8676,7 +8688,7 @@
       <c r="I33" t="n">
         <v>2.69</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42667</v>
       </c>
       <c r="K33" t="n">
@@ -8689,13 +8701,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8722,7 +8734,7 @@
       <c r="I34" t="n">
         <v>2.77</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="K34" t="n">
@@ -8735,13 +8747,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8768,7 +8780,7 @@
       <c r="I35" t="n">
         <v>2.56</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="K35" t="n">
@@ -8781,13 +8793,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8814,7 +8826,7 @@
       <c r="I36" t="n">
         <v>2.67</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K36" t="n">
@@ -8827,13 +8839,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8860,7 +8872,7 @@
       <c r="I37" t="n">
         <v>2.68</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K37" t="n">
@@ -8873,13 +8885,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8906,7 +8918,7 @@
       <c r="I38" t="n">
         <v>2.74</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="K38" t="n">
@@ -8919,13 +8931,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8952,7 +8964,7 @@
       <c r="I39" t="n">
         <v>3.22</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="K39" t="n">
@@ -8965,13 +8977,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8998,7 +9010,7 @@
       <c r="I40" t="n">
         <v>3.44</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K40" t="n">
@@ -9011,13 +9023,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9044,7 +9056,7 @@
       <c r="I41" t="n">
         <v>3.71</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K41" t="n">
@@ -9057,13 +9069,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9090,7 +9102,7 @@
       <c r="I42" t="n">
         <v>3.91</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K42" t="n">
@@ -9103,13 +9115,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9136,7 +9148,7 @@
       <c r="I43" t="n">
         <v>3.94</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K43" t="n">
@@ -9149,13 +9161,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9182,7 +9194,7 @@
       <c r="I44" t="n">
         <v>4.04</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K44" t="n">
@@ -9195,13 +9207,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9228,7 +9240,7 @@
       <c r="I45" t="n">
         <v>3.98</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="K45" t="n">
@@ -9241,13 +9253,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43893</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9274,7 +9286,7 @@
       <c r="I46" t="n">
         <v>3.71</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43893</v>
       </c>
       <c r="K46" t="n">
@@ -9287,13 +9299,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9320,7 +9332,7 @@
       <c r="I47" t="n">
         <v>3.470000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="K47" t="n">
@@ -9333,13 +9345,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9366,7 +9378,7 @@
       <c r="I48" t="n">
         <v>3.05</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="K48" t="n">
@@ -9379,13 +9391,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9412,7 +9424,7 @@
       <c r="I49" t="n">
         <v>2.890000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="K49" t="n">
@@ -9425,13 +9437,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9458,7 +9470,7 @@
       <c r="I50" t="n">
         <v>3.080000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="K50" t="n">
@@ -9471,13 +9483,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44319</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9504,7 +9516,7 @@
       <c r="I51" t="n">
         <v>3.330000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44319</v>
       </c>
       <c r="K51" t="n">
@@ -9517,13 +9529,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9550,7 +9562,7 @@
       <c r="I52" t="n">
         <v>3.82</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K52" t="n">
@@ -9563,13 +9575,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9596,7 +9608,7 @@
       <c r="I53" t="n">
         <v>4.23</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="K53" t="n">
@@ -9609,13 +9621,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9642,7 +9654,7 @@
       <c r="I54" t="n">
         <v>4.47</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="K54" t="n">
@@ -9655,13 +9667,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9688,7 +9700,7 @@
       <c r="I55" t="n">
         <v>4.48</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K55" t="n">
@@ -9701,13 +9713,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9734,7 +9746,7 @@
       <c r="I56" t="n">
         <v>4.41</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="K56" t="n">
@@ -9747,13 +9759,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9780,7 +9792,7 @@
       <c r="I57" t="n">
         <v>4.359999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="K57" t="n">
@@ -9793,13 +9805,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9826,7 +9838,7 @@
       <c r="I58" t="n">
         <v>4.43</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="K58" t="n">
@@ -9839,13 +9851,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9872,7 +9884,7 @@
       <c r="I59" t="n">
         <v>4.49</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="K59" t="n">
@@ -9885,13 +9897,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9918,7 +9930,7 @@
       <c r="I60" t="n">
         <v>4.32</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="K60" t="n">
@@ -9931,13 +9943,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9964,7 +9976,7 @@
       <c r="I61" t="n">
         <v>3.97</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K61" t="n">
@@ -9977,13 +9989,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10010,7 +10022,7 @@
       <c r="I62" t="n">
         <v>-1.09</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="K62" t="n">
@@ -10023,13 +10035,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45421</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10056,7 +10068,7 @@
       <c r="I63" t="n">
         <v>-1.33</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45421</v>
       </c>
       <c r="K63" t="n">
@@ -10069,13 +10081,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10102,7 +10114,7 @@
       <c r="I64" t="n">
         <v>-1.63</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="K64" t="n">
@@ -10115,13 +10127,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10148,7 +10160,7 @@
       <c r="I65" t="n">
         <v>-1.44</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K65" t="n">
@@ -10161,13 +10173,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10194,7 +10206,7 @@
       <c r="I66" t="n">
         <v>3.36</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="K66" t="n">
@@ -10207,13 +10219,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10240,7 +10252,7 @@
       <c r="I67" t="n">
         <v>3.42</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="K67" t="n">
@@ -10253,13 +10265,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10286,7 +10298,7 @@
       <c r="I68" t="n">
         <v>3.7</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K68" t="n">
@@ -10299,13 +10311,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10332,7 +10344,7 @@
       <c r="I69" t="n">
         <v>3.75</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K69" t="n">
@@ -10345,13 +10357,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10378,7 +10390,7 @@
       <c r="I70" t="n">
         <v>3.82</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="K70" t="n">
@@ -10391,13 +10403,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10424,7 +10436,7 @@
       <c r="I71" t="n">
         <v>4.04</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K71" t="n">
@@ -10437,13 +10449,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10470,7 +10482,7 @@
       <c r="I72" t="n">
         <v>4.37</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K72" t="n">
@@ -10507,52 +10519,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="C2" t="n">
@@ -10581,10 +10593,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C3" t="n">
@@ -10613,10 +10625,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C4" t="n">
@@ -10645,10 +10657,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40423</v>
       </c>
       <c r="C5" t="n">
@@ -10677,10 +10689,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40491</v>
       </c>
       <c r="C6" t="n">
@@ -10709,10 +10721,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C7" t="n">
@@ -10741,10 +10753,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C8" t="n">
@@ -10773,10 +10785,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="C9" t="n">
@@ -10805,10 +10817,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="C10" t="n">
@@ -10837,10 +10849,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="C11" t="n">
@@ -10869,10 +10881,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="C12" t="n">
@@ -10901,10 +10913,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C13" t="n">
@@ -10933,10 +10945,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C14" t="n">
@@ -10965,10 +10977,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C15" t="n">
@@ -10997,10 +11009,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C16" t="n">
@@ -11029,10 +11041,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C17" t="n">
@@ -11061,10 +11073,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="C18" t="n">
@@ -11093,10 +11105,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="C19" t="n">
@@ -11125,10 +11137,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="C20" t="n">
@@ -11157,10 +11169,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41848</v>
       </c>
       <c r="C21" t="n">
@@ -11189,10 +11201,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41939</v>
       </c>
       <c r="C22" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C23" t="n">
@@ -11253,10 +11265,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42121</v>
       </c>
       <c r="C24" t="n">
@@ -11285,10 +11297,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="C25" t="n">
@@ -11317,10 +11329,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C26" t="n">
@@ -11349,10 +11361,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C27" t="n">
@@ -11381,10 +11393,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="C28" t="n">
@@ -11413,10 +11425,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C29" t="n">
@@ -11445,10 +11457,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42667</v>
       </c>
       <c r="C30" t="n">
@@ -11477,10 +11489,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="C31" t="n">
@@ -11509,10 +11521,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42849</v>
       </c>
       <c r="C32" t="n">
@@ -11541,10 +11553,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C33" t="n">
@@ -11573,10 +11585,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C34" t="n">
@@ -11605,10 +11617,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="C35" t="n">
@@ -11637,10 +11649,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="C36" t="n">
@@ -11669,10 +11681,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C37" t="n">
@@ -11701,10 +11713,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C38" t="n">
@@ -11733,10 +11745,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="C39" t="n">
@@ -11765,10 +11777,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C40" t="n">
@@ -11797,10 +11809,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C41" t="n">
@@ -11829,10 +11841,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="C42" t="n">
@@ -11861,10 +11873,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43893</v>
       </c>
       <c r="C43" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="C44" t="n">
@@ -11925,10 +11937,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="C45" t="n">
@@ -11957,10 +11969,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="C46" t="n">
@@ -11989,10 +12001,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="C47" t="n">
@@ -12021,10 +12033,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44319</v>
       </c>
       <c r="C48" t="n">
@@ -12053,10 +12065,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C49" t="n">
@@ -12085,10 +12097,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="C50" t="n">
@@ -12117,10 +12129,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C51" t="n">
@@ -12149,10 +12161,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C52" t="n">
@@ -12181,10 +12193,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="C53" t="n">
@@ -12213,10 +12225,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="C54" t="n">
@@ -12245,10 +12257,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="C55" t="n">
@@ -12277,10 +12289,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="C56" t="n">
@@ -12309,10 +12321,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="C57" t="n">
@@ -12341,10 +12353,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C58" t="n">
@@ -12373,10 +12385,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="C59" t="n">
@@ -12405,10 +12417,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45421</v>
       </c>
       <c r="C60" t="n">
@@ -12437,10 +12449,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="C61" t="n">
@@ -12469,10 +12481,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C62" t="n">
@@ -12501,10 +12513,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="C63" t="n">
@@ -12533,10 +12545,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="C64" t="n">
@@ -12565,10 +12577,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C65" t="n">
@@ -12597,10 +12609,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C66" t="n">
@@ -12629,10 +12641,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="C67" t="n">
@@ -12661,10 +12673,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C68" t="n">
@@ -12693,10 +12705,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="C69" t="n">
@@ -12743,12 +12755,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/TFC.xlsx
+++ b/salidas/empresas/TFC.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>17.78287124633789</v>
+        <v>17.78286933898926</v>
       </c>
       <c r="C2" t="n">
         <v>39.04000091552734</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>18.00606727600098</v>
+        <v>18.00607490539551</v>
       </c>
       <c r="C3" t="n">
         <v>39.52999877929688</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>17.85575675964355</v>
+        <v>17.85574913024902</v>
       </c>
       <c r="C4" t="n">
         <v>39.20000076293945</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>19.74603271484375</v>
+        <v>19.74603843688965</v>
       </c>
       <c r="C5" t="n">
         <v>42.93999862670898</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>19.11603927612305</v>
+        <v>19.11604118347168</v>
       </c>
       <c r="C6" t="n">
         <v>41.56999969482422</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>19.12523651123047</v>
+        <v>19.12524223327637</v>
       </c>
       <c r="C7" t="n">
         <v>41.59000015258789</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>19.50781059265137</v>
+        <v>19.5078067779541</v>
       </c>
       <c r="C8" t="n">
         <v>41.9900016784668</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>19.88411712646484</v>
+        <v>19.88412094116211</v>
       </c>
       <c r="C9" t="n">
         <v>42.79999923706055</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.33940696716309</v>
+        <v>20.33940887451172</v>
       </c>
       <c r="C10" t="n">
         <v>43.77999877929688</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.41244316101074</v>
+        <v>20.41244506835938</v>
       </c>
       <c r="C11" t="n">
         <v>43.52000045776367</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>20.17323112487793</v>
+        <v>20.17324638366699</v>
       </c>
       <c r="C12" t="n">
         <v>43.0099983215332</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.60474967956543</v>
+        <v>20.60475540161133</v>
       </c>
       <c r="C13" t="n">
         <v>43.93000030517578</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>20.01775932312012</v>
+        <v>20.01776504516602</v>
       </c>
       <c r="C14" t="n">
         <v>42.2599983215332</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>20.10776138305664</v>
+        <v>20.10776519775391</v>
       </c>
       <c r="C15" t="n">
         <v>42.45000076293945</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>19.43039703369141</v>
+        <v>19.43039321899414</v>
       </c>
       <c r="C16" t="n">
         <v>41.02000045776367</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>19.92000770568848</v>
+        <v>19.92000579833984</v>
       </c>
       <c r="C17" t="n">
         <v>41.61999893188477</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>20.1545352935791</v>
+        <v>20.1545295715332</v>
       </c>
       <c r="C18" t="n">
         <v>42.11000061035156</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>19.47011566162109</v>
+        <v>19.47011947631836</v>
       </c>
       <c r="C19" t="n">
         <v>40.68000030517578</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>19.23553657531738</v>
+        <v>19.23552894592285</v>
       </c>
       <c r="C21" t="n">
         <v>39.72999954223633</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>19.55507850646973</v>
+        <v>19.55508804321289</v>
       </c>
       <c r="C22" t="n">
         <v>40.38999938964844</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>18.09723281860352</v>
+        <v>18.09723472595215</v>
       </c>
       <c r="C23" t="n">
         <v>36.97000122070312</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>17.66157150268555</v>
+        <v>17.66156959533691</v>
       </c>
       <c r="C24" t="n">
         <v>36.08000183105469</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>15.01331233978271</v>
+        <v>15.01331424713135</v>
       </c>
       <c r="C25" t="n">
         <v>30.67000007629395</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>15.50381469726562</v>
+        <v>15.50380706787109</v>
       </c>
       <c r="C27" t="n">
         <v>31.1299991607666</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>17.31579780578613</v>
+        <v>17.3157901763916</v>
       </c>
       <c r="C29" t="n">
         <v>34.29000091552734</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>15.89175033569336</v>
+        <v>15.89174747467041</v>
       </c>
       <c r="C30" t="n">
         <v>31.46999931335449</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>11.49841022491455</v>
+        <v>11.49841403961182</v>
       </c>
       <c r="C31" t="n">
         <v>22.77000045776367</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>14.43303775787354</v>
+        <v>14.43303489685059</v>
       </c>
       <c r="C32" t="n">
         <v>28.02000045776367</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>18.72204780578613</v>
+        <v>18.72205352783203</v>
       </c>
       <c r="C35" t="n">
         <v>35.84999847412109</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>15.65132331848145</v>
+        <v>15.65131759643555</v>
       </c>
       <c r="C36" t="n">
         <v>29.96999931335449</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.34051322937012</v>
+        <v>14.34051418304443</v>
       </c>
       <c r="C37" t="n">
         <v>27.45999908447266</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>10.52766799926758</v>
+        <v>10.52766513824463</v>
       </c>
       <c r="C38" t="n">
         <v>19.79000091552734</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.580658912658691</v>
+        <v>8.580657958984375</v>
       </c>
       <c r="C39" t="n">
         <v>16.1299991607666</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>12.76166152954102</v>
+        <v>12.76166248321533</v>
       </c>
       <c r="C41" t="n">
         <v>23.34000015258789</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>12.0180549621582</v>
+        <v>12.01805305480957</v>
       </c>
       <c r="C43" t="n">
         <v>21.97999954223633</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>15.38757514953613</v>
+        <v>15.3875675201416</v>
       </c>
       <c r="C45" t="n">
         <v>27.94000053405762</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>15.00205326080322</v>
+        <v>15.00205612182617</v>
       </c>
       <c r="C46" t="n">
         <v>27.23999977111816</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>13.78780746459961</v>
+        <v>13.78780555725098</v>
       </c>
       <c r="C48" t="n">
         <v>24.89999961853027</v>
@@ -1422,7 +1422,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>15.52130126953125</v>
+        <v>15.52130508422852</v>
       </c>
       <c r="C50" t="n">
         <v>27.8700008392334</v>
@@ -1447,7 +1447,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>15.88887691497803</v>
+        <v>15.88887596130371</v>
       </c>
       <c r="C51" t="n">
         <v>28.53000068664551</v>
@@ -1472,7 +1472,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>18.03857612609863</v>
+        <v>18.03857803344727</v>
       </c>
       <c r="C52" t="n">
         <v>32.38999938964844</v>
@@ -1522,7 +1522,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>16.91688537597656</v>
+        <v>16.91688919067383</v>
       </c>
       <c r="C54" t="n">
         <v>30.23999977111816</v>
@@ -1547,7 +1547,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.71835899353027</v>
+        <v>14.71836471557617</v>
       </c>
       <c r="C55" t="n">
         <v>26.30999946594238</v>
@@ -1572,7 +1572,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>13.96939945220947</v>
+        <v>13.96940326690674</v>
       </c>
       <c r="C56" t="n">
         <v>24.82999992370605</v>
@@ -1597,7 +1597,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>12.44474983215332</v>
+        <v>12.44475269317627</v>
       </c>
       <c r="C57" t="n">
         <v>22.1200008392334</v>
@@ -1622,7 +1622,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>13.54745388031006</v>
+        <v>13.54744625091553</v>
       </c>
       <c r="C58" t="n">
         <v>24.07999992370605</v>
@@ -1672,7 +1672,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>13.13507843017578</v>
+        <v>13.13507652282715</v>
       </c>
       <c r="C60" t="n">
         <v>23.20000076293945</v>
@@ -1697,7 +1697,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>14.8845272064209</v>
+        <v>14.88452625274658</v>
       </c>
       <c r="C61" t="n">
         <v>26.29000091552734</v>
@@ -1722,7 +1722,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>15.73680973052979</v>
+        <v>15.73680114746094</v>
       </c>
       <c r="C62" t="n">
         <v>27.63999938964844</v>
@@ -1776,7 +1776,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>15.62863063812256</v>
+        <v>15.62863349914551</v>
       </c>
       <c r="C64" t="n">
         <v>27.45000076293945</v>
@@ -1805,7 +1805,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>15.42238903045654</v>
+        <v>15.42238140106201</v>
       </c>
       <c r="C65" t="n">
         <v>26.92000007629395</v>
@@ -1834,7 +1834,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>15.77758121490479</v>
+        <v>15.77757740020752</v>
       </c>
       <c r="C66" t="n">
         <v>27.54000091552734</v>
@@ -1863,7 +1863,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>15.37655353546143</v>
+        <v>15.37654876708984</v>
       </c>
       <c r="C67" t="n">
         <v>26.84000015258789</v>
@@ -1892,7 +1892,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>14.79926776885986</v>
+        <v>14.79927158355713</v>
       </c>
       <c r="C68" t="n">
         <v>25.68000030517578</v>
@@ -1921,7 +1921,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>12.84562683105469</v>
+        <v>12.84562301635742</v>
       </c>
       <c r="C69" t="n">
         <v>22.29000091552734</v>
@@ -1950,7 +1950,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>12.29238128662109</v>
+        <v>12.29238510131836</v>
       </c>
       <c r="C70" t="n">
         <v>21.32999992370605</v>
@@ -1979,7 +1979,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>13.54750633239746</v>
+        <v>13.54751014709473</v>
       </c>
       <c r="C71" t="n">
         <v>23.34000015258789</v>
@@ -2008,7 +2008,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>13.44883346557617</v>
+        <v>13.44883155822754</v>
       </c>
       <c r="C72" t="n">
         <v>23.17000007629395</v>
@@ -2037,7 +2037,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>14.60971355438232</v>
+        <v>14.60971260070801</v>
       </c>
       <c r="C73" t="n">
         <v>25.17000007629395</v>
@@ -2066,7 +2066,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>15.88046550750732</v>
+        <v>15.88046169281006</v>
       </c>
       <c r="C74" t="n">
         <v>27.19000053405762</v>
@@ -2095,7 +2095,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>17.08360862731934</v>
+        <v>17.08361434936523</v>
       </c>
       <c r="C75" t="n">
         <v>29.25</v>
@@ -2124,7 +2124,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>18.33349227905273</v>
+        <v>18.3334903717041</v>
       </c>
       <c r="C76" t="n">
         <v>31.38999938964844</v>
@@ -2153,7 +2153,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>18.83197784423828</v>
+        <v>18.83198547363281</v>
       </c>
       <c r="C77" t="n">
         <v>32.04000091552734</v>
@@ -2182,7 +2182,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>17.76224708557129</v>
+        <v>17.76225662231445</v>
       </c>
       <c r="C78" t="n">
         <v>30.21999931335449</v>
@@ -2211,7 +2211,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>18.13253784179688</v>
+        <v>18.13253974914551</v>
       </c>
       <c r="C79" t="n">
         <v>30.85000038146973</v>
@@ -2240,7 +2240,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.5574779510498</v>
+        <v>18.55748176574707</v>
       </c>
       <c r="C80" t="n">
         <v>31.3700008392334</v>
@@ -2269,7 +2269,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>18.65805053710938</v>
+        <v>18.65804290771484</v>
       </c>
       <c r="C81" t="n">
         <v>31.54000091552734</v>
@@ -2298,7 +2298,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>19.61638450622559</v>
+        <v>19.61638069152832</v>
       </c>
       <c r="C82" t="n">
         <v>33.15999984741211</v>
@@ -2327,7 +2327,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.23031234741211</v>
+        <v>17.23031806945801</v>
       </c>
       <c r="C83" t="n">
         <v>28.95000076293945</v>
@@ -2356,7 +2356,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>16.76607513427734</v>
+        <v>16.76607704162598</v>
       </c>
       <c r="C84" t="n">
         <v>28.17000007629395</v>
@@ -2385,7 +2385,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>17.32554244995117</v>
+        <v>17.32553863525391</v>
       </c>
       <c r="C85" t="n">
         <v>29.11000061035156</v>
@@ -2414,7 +2414,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>18.14657402038574</v>
+        <v>18.14657211303711</v>
       </c>
       <c r="C86" t="n">
         <v>30.28000068664551</v>
@@ -2443,7 +2443,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>18.3304271697998</v>
+        <v>18.33042907714844</v>
       </c>
       <c r="C87" t="n">
         <v>30.36000061035156</v>
@@ -2472,7 +2472,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>18.95231056213379</v>
+        <v>18.95230865478516</v>
       </c>
       <c r="C88" t="n">
         <v>31.38999938964844</v>
@@ -2501,7 +2501,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>18.57797241210938</v>
+        <v>18.57797622680664</v>
       </c>
       <c r="C89" t="n">
         <v>30.77000045776367</v>
@@ -2530,7 +2530,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>20.02221488952637</v>
+        <v>20.022216796875</v>
       </c>
       <c r="C90" t="n">
         <v>32.91999816894531</v>
@@ -2559,7 +2559,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>20.60610389709473</v>
+        <v>20.60610198974609</v>
       </c>
       <c r="C91" t="n">
         <v>33.88000106811523</v>
@@ -2588,7 +2588,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>21.70695686340332</v>
+        <v>21.70696258544922</v>
       </c>
       <c r="C92" t="n">
         <v>35.68999862670898</v>
@@ -2617,7 +2617,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>20.78726959228516</v>
+        <v>20.78727340698242</v>
       </c>
       <c r="C93" t="n">
         <v>33.95999908447266</v>
@@ -2646,7 +2646,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>20.65872955322266</v>
+        <v>20.65873146057129</v>
       </c>
       <c r="C94" t="n">
         <v>33.75</v>
@@ -2675,7 +2675,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>20.79339218139648</v>
+        <v>20.79339408874512</v>
       </c>
       <c r="C95" t="n">
         <v>33.97000122070312</v>
@@ -2704,7 +2704,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>21.41101837158203</v>
+        <v>21.41102409362793</v>
       </c>
       <c r="C96" t="n">
         <v>34.7400016784668</v>
@@ -2733,7 +2733,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>23.00113296508789</v>
+        <v>23.00113105773926</v>
       </c>
       <c r="C97" t="n">
         <v>37.31999969482422</v>
@@ -2762,7 +2762,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>23.05659484863281</v>
+        <v>23.05660629272461</v>
       </c>
       <c r="C98" t="n">
         <v>37.40999984741211</v>
@@ -2791,7 +2791,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>23.44026947021484</v>
+        <v>23.44027900695801</v>
       </c>
       <c r="C99" t="n">
         <v>37.79999923706055</v>
@@ -2820,7 +2820,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>24.90994071960449</v>
+        <v>24.90994453430176</v>
       </c>
       <c r="C100" t="n">
         <v>40.16999816894531</v>
@@ -2849,7 +2849,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>23.14882278442383</v>
+        <v>23.1488208770752</v>
       </c>
       <c r="C101" t="n">
         <v>37.33000183105469</v>
@@ -2878,7 +2878,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>23.66454124450684</v>
+        <v>23.66453552246094</v>
       </c>
       <c r="C102" t="n">
         <v>37.91999816894531</v>
@@ -2907,7 +2907,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>24.60688018798828</v>
+        <v>24.60687828063965</v>
       </c>
       <c r="C103" t="n">
         <v>39.43000030517578</v>
@@ -2936,7 +2936,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>23.10287094116211</v>
+        <v>23.10288238525391</v>
       </c>
       <c r="C104" t="n">
         <v>37.02000045776367</v>
@@ -2965,7 +2965,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>23.45074462890625</v>
+        <v>23.45075416564941</v>
       </c>
       <c r="C105" t="n">
         <v>37.33000183105469</v>
@@ -2994,7 +2994,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>23.37536239624023</v>
+        <v>23.37536811828613</v>
       </c>
       <c r="C106" t="n">
         <v>37.20999908447266</v>
@@ -3052,7 +3052,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>23.76449775695801</v>
+        <v>23.76449394226074</v>
       </c>
       <c r="C108" t="n">
         <v>37.59000015258789</v>
@@ -3081,7 +3081,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>24.58634948730469</v>
+        <v>24.58635520935059</v>
       </c>
       <c r="C109" t="n">
         <v>38.88999938964844</v>
@@ -3110,7 +3110,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>22.31042671203613</v>
+        <v>22.31042098999023</v>
       </c>
       <c r="C110" t="n">
         <v>35.29000091552734</v>
@@ -3139,7 +3139,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>24.20896911621094</v>
+        <v>24.20897102355957</v>
       </c>
       <c r="C111" t="n">
         <v>38.04999923706055</v>
@@ -3168,7 +3168,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>24.80703926086426</v>
+        <v>24.80703544616699</v>
       </c>
       <c r="C112" t="n">
         <v>38.9900016784668</v>
@@ -3226,7 +3226,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>25.28695487976074</v>
+        <v>25.28696060180664</v>
       </c>
       <c r="C114" t="n">
         <v>39.47000122070312</v>
@@ -3284,7 +3284,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>25.79949378967285</v>
+        <v>25.79949188232422</v>
       </c>
       <c r="C116" t="n">
         <v>40.27000045776367</v>
@@ -3313,7 +3313,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>23.81316947937012</v>
+        <v>23.81316757202148</v>
       </c>
       <c r="C117" t="n">
         <v>36.91999816894531</v>
@@ -3342,7 +3342,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>22.96178245544434</v>
+        <v>22.9617805480957</v>
       </c>
       <c r="C118" t="n">
         <v>35.59999847412109</v>
@@ -3371,7 +3371,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>23.96152877807617</v>
+        <v>23.96151733398438</v>
       </c>
       <c r="C119" t="n">
         <v>37.15000152587891</v>
@@ -3400,7 +3400,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>25.08489799499512</v>
+        <v>25.08489990234375</v>
       </c>
       <c r="C120" t="n">
         <v>38.61999893188477</v>
@@ -3429,7 +3429,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>24.55877876281738</v>
+        <v>24.55877494812012</v>
       </c>
       <c r="C121" t="n">
         <v>37.81000137329102</v>
@@ -3458,7 +3458,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>21.21369934082031</v>
+        <v>21.21368980407715</v>
       </c>
       <c r="C122" t="n">
         <v>32.65999984741211</v>
@@ -3487,7 +3487,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>21.06895065307617</v>
+        <v>21.06893920898438</v>
       </c>
       <c r="C123" t="n">
         <v>32.15999984741211</v>
@@ -3516,7 +3516,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>21.796142578125</v>
+        <v>21.79614067077637</v>
       </c>
       <c r="C124" t="n">
         <v>33.27000045776367</v>
@@ -3545,7 +3545,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>23.1784553527832</v>
+        <v>23.17846298217773</v>
       </c>
       <c r="C125" t="n">
         <v>35.38000106811523</v>
@@ -3574,7 +3574,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>24.02268600463867</v>
+        <v>24.02268981933594</v>
       </c>
       <c r="C126" t="n">
         <v>36.36999893188477</v>
@@ -3603,7 +3603,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>23.52070045471191</v>
+        <v>23.52070808410645</v>
       </c>
       <c r="C127" t="n">
         <v>35.61000061035156</v>
@@ -3632,7 +3632,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>24.35293579101562</v>
+        <v>24.35294342041016</v>
       </c>
       <c r="C128" t="n">
         <v>36.86999893188477</v>
@@ -3690,7 +3690,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>25.11263465881348</v>
+        <v>25.11262702941895</v>
       </c>
       <c r="C130" t="n">
         <v>37.72000122070312</v>
@@ -3719,7 +3719,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>26.09796905517578</v>
+        <v>26.09796714782715</v>
       </c>
       <c r="C131" t="n">
         <v>39.20000076293945</v>
@@ -3748,7 +3748,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>30.35732841491699</v>
+        <v>30.35733222961426</v>
       </c>
       <c r="C132" t="n">
         <v>45.25</v>
@@ -3777,7 +3777,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>31.5447998046875</v>
+        <v>31.54477882385254</v>
       </c>
       <c r="C133" t="n">
         <v>47.02000045776367</v>
@@ -3835,7 +3835,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>32.56040954589844</v>
+        <v>32.5604248046875</v>
       </c>
       <c r="C135" t="n">
         <v>48.22000122070312</v>
@@ -3864,7 +3864,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>30.18354797363281</v>
+        <v>30.18355178833008</v>
       </c>
       <c r="C136" t="n">
         <v>44.70000076293945</v>
@@ -3893,7 +3893,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>29.15716552734375</v>
+        <v>29.15716934204102</v>
       </c>
       <c r="C137" t="n">
         <v>43.18000030517578</v>
@@ -3922,7 +3922,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>28.31948089599609</v>
+        <v>28.31949043273926</v>
       </c>
       <c r="C138" t="n">
         <v>41.65000152587891</v>
@@ -3951,7 +3951,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>30.87605857849121</v>
+        <v>30.87606430053711</v>
       </c>
       <c r="C139" t="n">
         <v>45.40999984741211</v>
@@ -4009,7 +4009,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>31.55422019958496</v>
+        <v>31.55423164367676</v>
       </c>
       <c r="C141" t="n">
         <v>46.09000015258789</v>
@@ -4038,7 +4038,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>32.13615798950195</v>
+        <v>32.13615417480469</v>
       </c>
       <c r="C142" t="n">
         <v>46.93999862670898</v>
@@ -4096,7 +4096,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>34.06947326660156</v>
+        <v>34.0694694519043</v>
       </c>
       <c r="C144" t="n">
         <v>49.41999816894531</v>
@@ -4154,7 +4154,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>38.0472412109375</v>
+        <v>38.0472297668457</v>
       </c>
       <c r="C146" t="n">
         <v>55.18999862670898</v>
@@ -4183,7 +4183,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>37.69930267333984</v>
+        <v>37.69929504394531</v>
       </c>
       <c r="C147" t="n">
         <v>54.34999847412109</v>
@@ -4241,7 +4241,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>36.65454483032227</v>
+        <v>36.654541015625</v>
       </c>
       <c r="C149" t="n">
         <v>52.79999923706055</v>
@@ -4270,7 +4270,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>36.69684219360352</v>
+        <v>36.69684982299805</v>
       </c>
       <c r="C150" t="n">
         <v>52.5</v>
@@ -4299,7 +4299,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>35.25693130493164</v>
+        <v>35.25693893432617</v>
       </c>
       <c r="C151" t="n">
         <v>50.43999862670898</v>
@@ -4328,7 +4328,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>35.51557159423828</v>
+        <v>35.51555633544922</v>
       </c>
       <c r="C152" t="n">
         <v>50.81000137329102</v>
@@ -4357,7 +4357,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>36.39310836791992</v>
+        <v>36.39308929443359</v>
       </c>
       <c r="C153" t="n">
         <v>51.65999984741211</v>
@@ -4415,7 +4415,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>34.63191223144531</v>
+        <v>34.63190078735352</v>
       </c>
       <c r="C155" t="n">
         <v>49.15999984741211</v>
@@ -4502,7 +4502,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>34.65817642211914</v>
+        <v>34.65818023681641</v>
       </c>
       <c r="C158" t="n">
         <v>48.79999923706055</v>
@@ -4531,7 +4531,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>36.49160003662109</v>
+        <v>36.49158477783203</v>
       </c>
       <c r="C159" t="n">
         <v>50.97000122070312</v>
@@ -4560,7 +4560,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>33.31281280517578</v>
+        <v>33.31280517578125</v>
       </c>
       <c r="C160" t="n">
         <v>46.52999877929688</v>
@@ -4589,7 +4589,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>36.65626525878906</v>
+        <v>36.6562614440918</v>
       </c>
       <c r="C161" t="n">
         <v>51.20000076293945</v>
@@ -4618,7 +4618,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>33.75375366210938</v>
+        <v>33.75376129150391</v>
       </c>
       <c r="C162" t="n">
         <v>46.75</v>
@@ -4676,7 +4676,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>37.20493698120117</v>
+        <v>37.20492935180664</v>
       </c>
       <c r="C164" t="n">
         <v>51.52999877929688</v>
@@ -4705,7 +4705,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>34.73858642578125</v>
+        <v>34.73859024047852</v>
       </c>
       <c r="C165" t="n">
         <v>47.65000152587891</v>
@@ -4763,7 +4763,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>38.67538452148438</v>
+        <v>38.67538070678711</v>
       </c>
       <c r="C167" t="n">
         <v>53.04999923706055</v>
@@ -4792,7 +4792,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>40.22045516967773</v>
+        <v>40.22046279907227</v>
       </c>
       <c r="C168" t="n">
         <v>54.72000122070312</v>
@@ -4850,7 +4850,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>37.90512466430664</v>
+        <v>37.9051399230957</v>
       </c>
       <c r="C170" t="n">
         <v>51.56999969482422</v>
@@ -4879,7 +4879,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>34.19663238525391</v>
+        <v>34.19662857055664</v>
       </c>
       <c r="C171" t="n">
         <v>46.13999938964844</v>
@@ -4908,7 +4908,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>22.85704612731934</v>
+        <v>22.85704231262207</v>
       </c>
       <c r="C172" t="n">
         <v>30.84000015258789</v>
@@ -4937,7 +4937,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>27.65968894958496</v>
+        <v>27.65969467163086</v>
       </c>
       <c r="C173" t="n">
         <v>37.31999969482422</v>
@@ -4966,7 +4966,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>27.65288734436035</v>
+        <v>27.65289306640625</v>
       </c>
       <c r="C174" t="n">
         <v>36.77999877929688</v>
@@ -5024,7 +5024,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>28.16414260864258</v>
+        <v>28.16414451599121</v>
       </c>
       <c r="C176" t="n">
         <v>37.45999908447266</v>
@@ -5053,7 +5053,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>29.50447082519531</v>
+        <v>29.50446891784668</v>
       </c>
       <c r="C177" t="n">
         <v>38.81000137329102</v>
@@ -5111,7 +5111,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>32.02082824707031</v>
+        <v>32.02082443237305</v>
       </c>
       <c r="C179" t="n">
         <v>42.11999893188477</v>
@@ -5140,7 +5140,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>35.61812973022461</v>
+        <v>35.61812210083008</v>
       </c>
       <c r="C180" t="n">
         <v>46.41999816894531</v>
@@ -5169,7 +5169,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>36.77674865722656</v>
+        <v>36.77675247192383</v>
       </c>
       <c r="C181" t="n">
         <v>47.93000030517578</v>
@@ -5198,7 +5198,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>36.81512069702148</v>
+        <v>36.81511306762695</v>
       </c>
       <c r="C182" t="n">
         <v>47.97999954223633</v>
@@ -5256,7 +5256,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>45.12710189819336</v>
+        <v>45.12709808349609</v>
       </c>
       <c r="C184" t="n">
         <v>58.31999969482422</v>
@@ -5285,7 +5285,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>45.89315414428711</v>
+        <v>45.89315032958984</v>
       </c>
       <c r="C185" t="n">
         <v>59.31000137329102</v>
@@ -5314,7 +5314,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>48.16801834106445</v>
+        <v>48.16801452636719</v>
       </c>
       <c r="C186" t="n">
         <v>61.77999877929688</v>
@@ -5343,7 +5343,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>43.27168273925781</v>
+        <v>43.27169418334961</v>
       </c>
       <c r="C187" t="n">
         <v>55.5</v>
@@ -5372,7 +5372,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>42.43744277954102</v>
+        <v>42.43744659423828</v>
       </c>
       <c r="C188" t="n">
         <v>54.43000030517578</v>
@@ -5401,7 +5401,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>44.8537483215332</v>
+        <v>44.85375213623047</v>
       </c>
       <c r="C189" t="n">
         <v>57.06000137329102</v>
@@ -5459,7 +5459,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>49.89252853393555</v>
+        <v>49.89253616333008</v>
       </c>
       <c r="C191" t="n">
         <v>63.47000122070312</v>
@@ -5488,7 +5488,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>46.97068023681641</v>
+        <v>46.97068786621094</v>
       </c>
       <c r="C192" t="n">
         <v>59.31000137329102</v>
@@ -5517,7 +5517,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>46.36881256103516</v>
+        <v>46.36880111694336</v>
       </c>
       <c r="C193" t="n">
         <v>58.54999923706055</v>
@@ -5546,7 +5546,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>49.75044631958008</v>
+        <v>49.75044250488281</v>
       </c>
       <c r="C194" t="n">
         <v>62.81999969482422</v>
@@ -5575,7 +5575,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>49.6390380859375</v>
+        <v>49.63904190063477</v>
       </c>
       <c r="C195" t="n">
         <v>62.22000122070312</v>
@@ -5604,7 +5604,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>45.23519515991211</v>
+        <v>45.23519897460938</v>
       </c>
       <c r="C196" t="n">
         <v>56.70000076293945</v>
@@ -5633,7 +5633,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>38.57357788085938</v>
+        <v>38.57356643676758</v>
       </c>
       <c r="C197" t="n">
         <v>48.34999847412109</v>
@@ -5662,7 +5662,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>40.09328842163086</v>
+        <v>40.09328079223633</v>
       </c>
       <c r="C198" t="n">
         <v>49.7400016784668</v>
@@ -5691,7 +5691,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>38.23129272460938</v>
+        <v>38.23128890991211</v>
       </c>
       <c r="C199" t="n">
         <v>47.43000030517578</v>
@@ -5749,7 +5749,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>38.14541625976562</v>
+        <v>38.14542007446289</v>
       </c>
       <c r="C201" t="n">
         <v>46.84000015258789</v>
@@ -5778,7 +5778,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>35.45797348022461</v>
+        <v>35.45796585083008</v>
       </c>
       <c r="C202" t="n">
         <v>43.54000091552734</v>
@@ -5807,7 +5807,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>36.4759407043457</v>
+        <v>36.47594451904297</v>
       </c>
       <c r="C203" t="n">
         <v>44.79000091552734</v>
@@ -5865,7 +5865,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>35.45705413818359</v>
+        <v>35.45706558227539</v>
       </c>
       <c r="C205" t="n">
         <v>43.02999877929688</v>
@@ -5923,7 +5923,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>39.09991836547852</v>
+        <v>39.09992599487305</v>
       </c>
       <c r="C207" t="n">
         <v>46.95000076293945</v>
@@ -5952,7 +5952,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>28.39845275878906</v>
+        <v>28.39845085144043</v>
       </c>
       <c r="C208" t="n">
         <v>34.09999847412109</v>
@@ -5981,7 +5981,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>27.13259887695312</v>
+        <v>27.13259696960449</v>
       </c>
       <c r="C209" t="n">
         <v>32.58000183105469</v>
@@ -6010,7 +6010,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>25.85732078552246</v>
+        <v>25.85731506347656</v>
       </c>
       <c r="C210" t="n">
         <v>30.46999931335449</v>
@@ -6039,7 +6039,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>25.75548553466797</v>
+        <v>25.75548362731934</v>
       </c>
       <c r="C211" t="n">
         <v>30.35000038146973</v>
@@ -6068,7 +6068,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>28.19100952148438</v>
+        <v>28.19101333618164</v>
       </c>
       <c r="C212" t="n">
         <v>33.22000122070312</v>
@@ -6126,7 +6126,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>24.68681144714355</v>
+        <v>24.68681335449219</v>
       </c>
       <c r="C214" t="n">
         <v>28.61000061035156</v>
@@ -6155,7 +6155,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>24.47109031677246</v>
+        <v>24.47109222412109</v>
       </c>
       <c r="C215" t="n">
         <v>28.36000061035156</v>
@@ -6184,7 +6184,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>28.21538734436035</v>
+        <v>28.21538543701172</v>
       </c>
       <c r="C216" t="n">
         <v>32.13999938964844</v>
@@ -6271,7 +6271,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>31.15853881835938</v>
+        <v>31.15854072570801</v>
       </c>
       <c r="C219" t="n">
         <v>34.97999954223633</v>
@@ -6298,7 +6298,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>34.72154235839844</v>
+        <v>34.7215461730957</v>
       </c>
       <c r="C220" t="n">
         <v>38.97999954223633</v>
@@ -6352,7 +6352,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>34.07575988769531</v>
+        <v>34.07576751708984</v>
       </c>
       <c r="C222" t="n">
         <v>37.75</v>
@@ -6379,7 +6379,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>35.06869888305664</v>
+        <v>35.06870269775391</v>
       </c>
       <c r="C223" t="n">
         <v>38.84999847412109</v>
@@ -6406,7 +6406,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>40.34028625488281</v>
+        <v>40.34029006958008</v>
       </c>
       <c r="C224" t="n">
         <v>44.68999862670898</v>
@@ -6460,7 +6460,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>39.09032821655273</v>
+        <v>39.09033584594727</v>
       </c>
       <c r="C226" t="n">
         <v>42.77000045776367</v>
@@ -6487,7 +6487,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>39.34624862670898</v>
+        <v>39.34624481201172</v>
       </c>
       <c r="C227" t="n">
         <v>43.04999923706055</v>
@@ -6541,7 +6541,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>40.09919357299805</v>
+        <v>40.09918975830078</v>
       </c>
       <c r="C229" t="n">
         <v>43.38000106811523</v>
@@ -6653,7 +6653,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>35.84151840209961</v>
+        <v>35.84151458740234</v>
       </c>
       <c r="C233" t="n">
         <v>38.34000015258789</v>
@@ -6682,7 +6682,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>37.41776275634766</v>
+        <v>37.41775894165039</v>
       </c>
       <c r="C234" t="n">
         <v>39.5</v>
@@ -6740,7 +6740,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>41.40583419799805</v>
+        <v>41.40583038330078</v>
       </c>
       <c r="C236" t="n">
         <v>43.70999908447266</v>
@@ -6827,7 +6827,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>42.79668426513672</v>
+        <v>42.79668807983398</v>
       </c>
       <c r="C239" t="n">
         <v>44.63000106811523</v>
@@ -6856,7 +6856,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>45.10731887817383</v>
+        <v>45.10731506347656</v>
       </c>
       <c r="C240" t="n">
         <v>46.5</v>
